--- a/PPM App Data.xlsx
+++ b/PPM App Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/928dbb3f54bde61d/Documents/AMC/PPM App final version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C626CB-3BE2-458A-A377-556AA8BAE2B8}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3BE876F-59C7-433E-BA90-8C9F66CF275B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1140" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Planning Updated" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="341">
   <si>
     <t>phone</t>
   </si>
@@ -979,6 +979,90 @@
   </si>
   <si>
     <t xml:space="preserve">L0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranjit Biswakarma </t>
+  </si>
+  <si>
+    <t>Jayaprasath</t>
+  </si>
+  <si>
+    <t>Helper</t>
+  </si>
+  <si>
+    <t>Jawthath</t>
+  </si>
+  <si>
+    <t>Siraf</t>
+  </si>
+  <si>
+    <t>Manjeet</t>
+  </si>
+  <si>
+    <t>Ranjit</t>
+  </si>
+  <si>
+    <t>Akbar</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Arvind</t>
+  </si>
+  <si>
+    <t>Azzarudhin</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>Geayash</t>
+  </si>
+  <si>
+    <t>habib</t>
+  </si>
+  <si>
+    <t>Hazrat</t>
+  </si>
+  <si>
+    <t>Majit</t>
+  </si>
+  <si>
+    <t>Musharaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saddam </t>
+  </si>
+  <si>
+    <t>Shah Faisal</t>
+  </si>
+  <si>
+    <t>Shazib</t>
+  </si>
+  <si>
+    <t>Umer</t>
+  </si>
+  <si>
+    <t>Waqas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sajid </t>
+  </si>
+  <si>
+    <t>Thovatoo</t>
+  </si>
+  <si>
+    <t>Lifco Sharjah -10/07/2025</t>
+  </si>
+  <si>
+    <t>AMC11378</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>DX</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1073,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,8 +1092,15 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1022,8 +1113,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1076,11 +1179,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1111,20 +1239,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{F18F3C03-5644-4A25-9F1D-61C4F6C009CC}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDDDDDD"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDDDDDD"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDDDDDD"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDDDDDD"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1137,6 +1313,40 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F4841A2-8693-45C3-9597-9D03C5C8F49F}" name="Table1" displayName="Table1" ref="B1:J26" totalsRowShown="0">
+  <autoFilter ref="B1:J26" xr:uid="{4F4841A2-8693-45C3-9597-9D03C5C8F49F}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{ACCBFABC-F80F-484E-969C-CBB87E1161BB}" name="Technician Name"/>
+    <tableColumn id="2" xr3:uid="{8ABFFE7F-51C2-4B2D-BAA9-8675DA857D60}" name="City"/>
+    <tableColumn id="3" xr3:uid="{0EC948ED-8149-447F-8339-7656034EDC8D}" name="Driver"/>
+    <tableColumn id="4" xr3:uid="{9261D1F2-00AB-4B3C-9B3B-F37AF00323A2}" name="Skill Level"/>
+    <tableColumn id="5" xr3:uid="{C4923CDD-7696-4BA4-A6C8-61F36E394978}" name="New Level"/>
+    <tableColumn id="6" xr3:uid="{3E7C7BEB-760A-48D3-A79E-13999FB59CFF}" name="Category" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{F70932DE-901A-4C53-BCEB-1026AC9D02A2}" name="Annual leave"/>
+    <tableColumn id="8" xr3:uid="{5AD73D7F-D94F-49F8-9AB4-E679687F11AE}" name="Project Owner" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{D9DA01A5-3502-48BA-BDBE-AED4753D3601}" name="Remark"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFF1069B-F0A8-4D84-81FE-E4558AA073D1}" name="Table2" displayName="Table2" ref="A1:C56" totalsRowShown="0">
+  <autoFilter ref="A1:C56" xr:uid="{EFF1069B-F0A8-4D84-81FE-E4558AA073D1}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{6D595F33-AE4B-43C0-89E6-0EBFA6C69C1F}" name="phone" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{D1C5B6C7-B7A7-4AF5-8A4B-FCA535AF4CCA}" name="name" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{C601CD76-EF83-4396-A8D0-C2451BFD2578}" name="role"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1424,7 +1634,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z72"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -1535,7 +1746,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1619,7 +1830,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1703,7 +1914,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1955,7 +2166,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -2039,7 +2250,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -2123,7 +2334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -2207,7 +2418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2291,7 +2502,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2375,7 +2586,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2459,7 +2670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2543,7 +2754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2627,7 +2838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2711,7 +2922,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2795,7 +3006,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2879,7 +3090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2963,7 +3174,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3047,7 +3258,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3131,7 +3342,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3215,7 +3426,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3299,7 +3510,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3383,7 +3594,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3464,7 +3675,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3545,7 +3756,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3626,7 +3837,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3710,7 +3921,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3794,7 +4005,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3878,7 +4089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3962,7 +4173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4040,7 +4251,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6952,7 +7163,7 @@
         <v>12</v>
       </c>
       <c r="Z66">
-        <f t="shared" ref="Z66:Z72" si="7">SUM(U66:X66)</f>
+        <f t="shared" ref="Z66:Z73" si="7">SUM(U66:X66)</f>
         <v>8</v>
       </c>
     </row>
@@ -7451,20 +7662,112 @@
         <v>8</v>
       </c>
     </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>337</v>
+      </c>
+      <c r="C73" t="s">
+        <v>51</v>
+      </c>
+      <c r="D73" t="s">
+        <v>338</v>
+      </c>
+      <c r="E73" t="s">
+        <v>114</v>
+      </c>
+      <c r="F73" s="5">
+        <v>46272</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>24</v>
+      </c>
+      <c r="I73" s="4">
+        <v>12</v>
+      </c>
+      <c r="J73" s="4">
+        <v>12</v>
+      </c>
+      <c r="K73" t="s">
+        <v>100</v>
+      </c>
+      <c r="L73" s="5">
+        <v>46082</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73">
+        <v>2026</v>
+      </c>
+      <c r="O73" t="s">
+        <v>339</v>
+      </c>
+      <c r="P73">
+        <v>2</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>63</v>
+      </c>
+      <c r="R73" t="s">
+        <v>94</v>
+      </c>
+      <c r="S73" t="s">
+        <v>58</v>
+      </c>
+      <c r="T73" t="s">
+        <v>340</v>
+      </c>
+      <c r="U73">
+        <v>151</v>
+      </c>
+      <c r="V73" s="23">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>151</v>
+      </c>
+      <c r="X73" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>12</v>
+      </c>
+      <c r="Z73">
+        <f>SUM(U73:Y73)</f>
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z72" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Z72" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Siva V"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:J20"/>
+  <dimension ref="B1:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="7" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
@@ -7951,19 +8254,39 @@
         <v>270</v>
       </c>
     </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:I16" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8258,18 +8581,18 @@
         <v>503285621</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>678901234</v>
+        <v>509288074</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -8297,8 +8620,297 @@
         <v>10</v>
       </c>
     </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/PPM App Data.xlsx
+++ b/PPM App Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/928dbb3f54bde61d/Documents/AMC/PPM App final version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3BE876F-59C7-433E-BA90-8C9F66CF275B}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECE61E0B-2092-4C59-860A-0AAF0F6351A9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1140" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Planning Updated" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Inputs" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Planning Updated'!$A$1:$Z$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Planning Updated'!$A$1:$Z$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Team!$B$1:$I$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="344">
   <si>
     <t>phone</t>
   </si>
@@ -1063,6 +1063,15 @@
   </si>
   <si>
     <t>DX</t>
+  </si>
+  <si>
+    <t>AMC11523</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>Luxe Hotel - Satwa - 15/01/2026</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1109,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1110,18 +1119,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1208,7 +1205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1239,34 +1236,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1634,7 +1610,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1746,7 +1721,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1830,7 +1805,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1914,7 +1889,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2166,7 +2141,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -2250,7 +2225,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -2334,7 +2309,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -2418,7 +2393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2502,7 +2477,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2586,7 +2561,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2670,7 +2645,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2754,7 +2729,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2838,7 +2813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2922,7 +2897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3006,7 +2981,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3090,7 +3065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3174,7 +3149,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3258,7 +3233,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3342,7 +3317,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3426,7 +3401,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3510,7 +3485,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3594,7 +3569,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3675,7 +3650,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3756,7 +3731,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3837,7 +3812,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3921,7 +3896,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4005,7 +3980,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4089,7 +4064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4173,7 +4148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4251,7 +4226,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7163,7 +7138,7 @@
         <v>12</v>
       </c>
       <c r="Z66">
-        <f t="shared" ref="Z66:Z73" si="7">SUM(U66:X66)</f>
+        <f t="shared" ref="Z66:Z72" si="7">SUM(U66:X66)</f>
         <v>8</v>
       </c>
     </row>
@@ -7726,13 +7701,13 @@
       <c r="U73">
         <v>151</v>
       </c>
-      <c r="V73" s="23">
+      <c r="V73" s="15">
         <v>0</v>
       </c>
       <c r="W73">
         <v>151</v>
       </c>
-      <c r="X73" s="23">
+      <c r="X73" s="15">
         <v>0</v>
       </c>
       <c r="Y73">
@@ -7744,13 +7719,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z72" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Siva V"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8621,288 +8589,288 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
+      <c r="A31" s="8">
         <v>123456789</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
+      <c r="A32" s="8">
         <v>123456789</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="14">
+      <c r="A33" s="8">
         <v>123456789</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
+      <c r="A34" s="8">
         <v>123456789</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="14">
+      <c r="A35" s="8">
         <v>123456789</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
+      <c r="A36" s="8">
         <v>123456789</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="14">
+      <c r="A37" s="8">
         <v>123456789</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
+      <c r="A38" s="8">
         <v>123456789</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="14">
+      <c r="A39" s="8">
         <v>123456789</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="14">
+      <c r="A40" s="8">
         <v>123456789</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="14">
+      <c r="A41" s="8">
         <v>123456789</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
+      <c r="A42" s="8">
         <v>123456789</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="14">
+      <c r="A43" s="8">
         <v>123456789</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="14">
+      <c r="A44" s="8">
         <v>123456789</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="14">
+      <c r="A45" s="8">
         <v>123456789</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="14">
+      <c r="A46" s="8">
         <v>123456789</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="14">
+      <c r="A47" s="8">
         <v>123456789</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="14">
+      <c r="A48" s="8">
         <v>123456789</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="14">
+      <c r="A49" s="8">
         <v>123456789</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="14">
+      <c r="A50" s="8">
         <v>123456789</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="14">
+      <c r="A51" s="8">
         <v>123456789</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="14">
+      <c r="A52" s="8">
         <v>123456789</v>
       </c>
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="14">
+      <c r="A53" s="8">
         <v>123456789</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="14">
+      <c r="A54" s="8">
         <v>123456789</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="14">
+      <c r="A55" s="8">
         <v>123456789</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="14">
+      <c r="A56" s="8">
         <v>123456789</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" t="s">
         <v>315</v>
       </c>
     </row>
@@ -8916,8 +8884,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
@@ -9201,6 +9185,478 @@
         <v>295</v>
       </c>
     </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" t="s">
+        <v>342</v>
+      </c>
+      <c r="N7" t="s">
+        <v>342</v>
+      </c>
+      <c r="O7" t="s">
+        <v>256</v>
+      </c>
+      <c r="P7" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>342</v>
+      </c>
+      <c r="R7">
+        <v>565265112</v>
+      </c>
+      <c r="S7" s="16">
+        <v>46083.491666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H8">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>264</v>
+      </c>
+      <c r="M8" t="s">
+        <v>342</v>
+      </c>
+      <c r="N8" t="s">
+        <v>342</v>
+      </c>
+      <c r="O8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P8" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>342</v>
+      </c>
+      <c r="R8">
+        <v>568325418</v>
+      </c>
+      <c r="S8" s="16">
+        <v>46083.744444444441</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>293</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>257</v>
+      </c>
+      <c r="M9" t="s">
+        <v>342</v>
+      </c>
+      <c r="N9" t="s">
+        <v>342</v>
+      </c>
+      <c r="O9" t="s">
+        <v>265</v>
+      </c>
+      <c r="P9" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>342</v>
+      </c>
+      <c r="R9">
+        <v>508656641</v>
+      </c>
+      <c r="S9" s="16">
+        <v>46083.818749999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>293</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>342</v>
+      </c>
+      <c r="M10" t="s">
+        <v>342</v>
+      </c>
+      <c r="N10" t="s">
+        <v>342</v>
+      </c>
+      <c r="O10" t="s">
+        <v>342</v>
+      </c>
+      <c r="P10" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>342</v>
+      </c>
+      <c r="R10">
+        <v>508656641</v>
+      </c>
+      <c r="S10" s="16">
+        <v>46083.818749999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>293</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>22</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>258</v>
+      </c>
+      <c r="M11" t="s">
+        <v>342</v>
+      </c>
+      <c r="N11" t="s">
+        <v>342</v>
+      </c>
+      <c r="O11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>342</v>
+      </c>
+      <c r="R11">
+        <v>569007478</v>
+      </c>
+      <c r="S11" s="16">
+        <v>46084.039583333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>293</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>342</v>
+      </c>
+      <c r="M12" t="s">
+        <v>342</v>
+      </c>
+      <c r="N12" t="s">
+        <v>342</v>
+      </c>
+      <c r="O12" t="s">
+        <v>269</v>
+      </c>
+      <c r="P12" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>342</v>
+      </c>
+      <c r="R12">
+        <v>509288074</v>
+      </c>
+      <c r="S12" s="16">
+        <v>46084.125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>293</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>342</v>
+      </c>
+      <c r="M13" t="s">
+        <v>342</v>
+      </c>
+      <c r="N13" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" t="s">
+        <v>269</v>
+      </c>
+      <c r="P13" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>342</v>
+      </c>
+      <c r="R13">
+        <v>509288074</v>
+      </c>
+      <c r="S13" s="16">
+        <v>46084.125694444447</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>269</v>
+      </c>
+      <c r="M14" t="s">
+        <v>342</v>
+      </c>
+      <c r="N14" t="s">
+        <v>342</v>
+      </c>
+      <c r="O14" t="s">
+        <v>342</v>
+      </c>
+      <c r="P14" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>342</v>
+      </c>
+      <c r="R14">
+        <v>509288074</v>
+      </c>
+      <c r="S14" s="16">
+        <v>46084.125694444447</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PPM App Data.xlsx
+++ b/PPM App Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/928dbb3f54bde61d/Documents/AMC/PPM App final version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECE61E0B-2092-4C59-860A-0AAF0F6351A9}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEBFE282-7CB4-4753-9C98-79822FEB6B28}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1140" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="344">
   <si>
     <t>phone</t>
   </si>
@@ -1296,8 +1296,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F4841A2-8693-45C3-9597-9D03C5C8F49F}" name="Table1" displayName="Table1" ref="B1:J26" totalsRowShown="0">
-  <autoFilter ref="B1:J26" xr:uid="{4F4841A2-8693-45C3-9597-9D03C5C8F49F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F4841A2-8693-45C3-9597-9D03C5C8F49F}" name="Table1" displayName="Table1" ref="B1:J70" totalsRowShown="0">
+  <autoFilter ref="B1:J70" xr:uid="{4F4841A2-8693-45C3-9597-9D03C5C8F49F}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{ACCBFABC-F80F-484E-969C-CBB87E1161BB}" name="Technician Name"/>
     <tableColumn id="2" xr3:uid="{8ABFFE7F-51C2-4B2D-BAA9-8675DA857D60}" name="City"/>
@@ -7725,7 +7725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:J26"/>
+  <dimension ref="B1:J70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -8223,22 +8223,454 @@
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
       <c r="I26" s="7"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G45" t="s">
+        <v>315</v>
+      </c>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="G46" t="s">
+        <v>315</v>
+      </c>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="G47" t="s">
+        <v>315</v>
+      </c>
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="G48" t="s">
+        <v>315</v>
+      </c>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="G49" t="s">
+        <v>315</v>
+      </c>
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="G50" t="s">
+        <v>315</v>
+      </c>
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="G51" t="s">
+        <v>315</v>
+      </c>
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="G52" t="s">
+        <v>315</v>
+      </c>
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="G53" t="s">
+        <v>315</v>
+      </c>
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="G54" t="s">
+        <v>315</v>
+      </c>
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B55" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G55" t="s">
+        <v>315</v>
+      </c>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B56" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="G56" t="s">
+        <v>315</v>
+      </c>
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B57" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="G57" t="s">
+        <v>315</v>
+      </c>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B58" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="G58" t="s">
+        <v>315</v>
+      </c>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B59" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G59" t="s">
+        <v>315</v>
+      </c>
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" t="s">
+        <v>315</v>
+      </c>
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B61" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="G61" t="s">
+        <v>315</v>
+      </c>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B62" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="G62" t="s">
+        <v>315</v>
+      </c>
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B63" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="G63" t="s">
+        <v>315</v>
+      </c>
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B64" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="G64" t="s">
+        <v>315</v>
+      </c>
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="G65" t="s">
+        <v>315</v>
+      </c>
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B66" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" t="s">
+        <v>315</v>
+      </c>
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="G67" t="s">
+        <v>315</v>
+      </c>
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="G68" t="s">
+        <v>315</v>
+      </c>
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B69" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" t="s">
+        <v>315</v>
+      </c>
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B70" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="G70" t="s">
+        <v>315</v>
+      </c>
+      <c r="I70" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PPM App Data.xlsx
+++ b/PPM App Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/928dbb3f54bde61d/Documents/AMC/PPM App final version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEBFE282-7CB4-4753-9C98-79822FEB6B28}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="11_CAC5AE23FA532E0C17336D9FB7EDAF85D093B3F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1503C57-904E-4EA5-BC52-87DAF539AF7A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1140" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="351">
   <si>
     <t>phone</t>
   </si>
@@ -1072,6 +1072,27 @@
   </si>
   <si>
     <t>Luxe Hotel - Satwa - 15/01/2026</t>
+  </si>
+  <si>
+    <t>Mr. Umesh Aggarwal Murooj V220- 01/10/2025</t>
+  </si>
+  <si>
+    <t>AMC11443</t>
+  </si>
+  <si>
+    <t>9/30/2026</t>
+  </si>
+  <si>
+    <t>1/14/2027</t>
+  </si>
+  <si>
+    <t>VRF;AHU;DX</t>
+  </si>
+  <si>
+    <t>56 221 8946</t>
+  </si>
+  <si>
+    <t>Ranjit Biswakarma</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1119,6 +1140,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1205,7 +1232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1243,6 +1270,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1610,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:Z75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -7718,6 +7748,168 @@
         <v>314</v>
       </c>
     </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="G74" s="17">
+        <v>3</v>
+      </c>
+      <c r="H74" s="17">
+        <v>3</v>
+      </c>
+      <c r="I74" s="17">
+        <v>12</v>
+      </c>
+      <c r="J74" s="17">
+        <v>3</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="L74" s="5">
+        <v>46082</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74">
+        <v>2026</v>
+      </c>
+      <c r="O74" t="s">
+        <v>339</v>
+      </c>
+      <c r="P74">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R74" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="S74" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="T74" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="U74" s="17">
+        <v>8</v>
+      </c>
+      <c r="V74" s="17">
+        <v>1</v>
+      </c>
+      <c r="W74" s="17">
+        <v>1</v>
+      </c>
+      <c r="X74" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y74" s="17">
+        <v>12</v>
+      </c>
+      <c r="Z74">
+        <f>SUM(U74:Y74)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="G75" s="17">
+        <v>4</v>
+      </c>
+      <c r="H75" s="17">
+        <v>27</v>
+      </c>
+      <c r="I75" s="17">
+        <v>12</v>
+      </c>
+      <c r="J75" s="17">
+        <v>27</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="L75" s="5">
+        <v>46082</v>
+      </c>
+      <c r="M75">
+        <v>2</v>
+      </c>
+      <c r="N75">
+        <v>2026</v>
+      </c>
+      <c r="O75" t="s">
+        <v>339</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="R75" t="s">
+        <v>94</v>
+      </c>
+      <c r="S75" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="T75" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="U75" s="17">
+        <v>154</v>
+      </c>
+      <c r="V75" s="17">
+        <v>36</v>
+      </c>
+      <c r="W75" s="17">
+        <v>15</v>
+      </c>
+      <c r="X75" s="17">
+        <v>4</v>
+      </c>
+      <c r="Y75" s="17">
+        <v>12</v>
+      </c>
+      <c r="Z75">
+        <f>SUM(U75:Y75)</f>
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9316,7 +9508,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -10030,63 +10222,1080 @@
         <v>46084.125694444447</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+    <row r="14" spans="1:19" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
         <v>46084</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="17">
         <v>2</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="H14" s="17">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17">
+        <v>0</v>
+      </c>
+      <c r="L14" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="M14" t="s">
-        <v>342</v>
-      </c>
-      <c r="N14" t="s">
-        <v>342</v>
-      </c>
-      <c r="O14" t="s">
-        <v>342</v>
-      </c>
-      <c r="P14" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>342</v>
-      </c>
-      <c r="R14">
+      <c r="M14" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="O14" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="R14" s="17">
         <v>509288074</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S14" s="19">
         <v>46084.125694444447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>342</v>
+      </c>
+      <c r="M15" t="s">
+        <v>342</v>
+      </c>
+      <c r="N15" t="s">
+        <v>342</v>
+      </c>
+      <c r="O15" t="s">
+        <v>342</v>
+      </c>
+      <c r="P15" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>342</v>
+      </c>
+      <c r="R15">
+        <v>565069985</v>
+      </c>
+      <c r="S15" s="16">
+        <v>46078.572372685187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>249</v>
+      </c>
+      <c r="M16" t="s">
+        <v>342</v>
+      </c>
+      <c r="N16" t="s">
+        <v>342</v>
+      </c>
+      <c r="O16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>342</v>
+      </c>
+      <c r="R16">
+        <v>565069985</v>
+      </c>
+      <c r="S16" s="16">
+        <v>46078.572511574072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="e">
+        <f>VLOOKUP(C17,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>289</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17" t="s">
+        <v>342</v>
+      </c>
+      <c r="M17" t="s">
+        <v>342</v>
+      </c>
+      <c r="N17" t="s">
+        <v>342</v>
+      </c>
+      <c r="O17" t="s">
+        <v>342</v>
+      </c>
+      <c r="P17" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>342</v>
+      </c>
+      <c r="R17">
+        <v>564227780</v>
+      </c>
+      <c r="S17" s="16">
+        <v>46078.573634259257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="e">
+        <f>VLOOKUP(C18,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>289</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" t="s">
+        <v>342</v>
+      </c>
+      <c r="N18" t="s">
+        <v>342</v>
+      </c>
+      <c r="O18" t="s">
+        <v>249</v>
+      </c>
+      <c r="P18" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>342</v>
+      </c>
+      <c r="R18">
+        <v>564227780</v>
+      </c>
+      <c r="S18" s="16">
+        <v>46078.573969907404</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>293</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" t="s">
+        <v>342</v>
+      </c>
+      <c r="N19" t="s">
+        <v>342</v>
+      </c>
+      <c r="O19" t="s">
+        <v>271</v>
+      </c>
+      <c r="P19" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>342</v>
+      </c>
+      <c r="R19">
+        <v>564227780</v>
+      </c>
+      <c r="S19" s="16">
+        <v>46078.585405092592</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20" t="e">
+        <f>VLOOKUP(C20,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>293</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>17</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" t="s">
+        <v>342</v>
+      </c>
+      <c r="N20" t="s">
+        <v>342</v>
+      </c>
+      <c r="O20" t="s">
+        <v>256</v>
+      </c>
+      <c r="P20" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>342</v>
+      </c>
+      <c r="R20">
+        <v>565265112</v>
+      </c>
+      <c r="S20" s="16">
+        <v>46083.491666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" t="e">
+        <f>VLOOKUP(C21,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>293</v>
+      </c>
+      <c r="H21">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>264</v>
+      </c>
+      <c r="M21" t="s">
+        <v>342</v>
+      </c>
+      <c r="N21" t="s">
+        <v>342</v>
+      </c>
+      <c r="O21" t="s">
+        <v>256</v>
+      </c>
+      <c r="P21" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>342</v>
+      </c>
+      <c r="R21">
+        <v>568325418</v>
+      </c>
+      <c r="S21" s="16">
+        <v>46083.744444444441</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" t="e">
+        <f>VLOOKUP(C22,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>293</v>
+      </c>
+      <c r="H22">
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
+        <v>257</v>
+      </c>
+      <c r="M22" t="s">
+        <v>342</v>
+      </c>
+      <c r="N22" t="s">
+        <v>342</v>
+      </c>
+      <c r="O22" t="s">
+        <v>265</v>
+      </c>
+      <c r="P22" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>342</v>
+      </c>
+      <c r="R22">
+        <v>508656641</v>
+      </c>
+      <c r="S22" s="16">
+        <v>46083.818749999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" t="e">
+        <f>VLOOKUP(C23,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>293</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="s">
+        <v>342</v>
+      </c>
+      <c r="M23" t="s">
+        <v>342</v>
+      </c>
+      <c r="N23" t="s">
+        <v>342</v>
+      </c>
+      <c r="O23" t="s">
+        <v>342</v>
+      </c>
+      <c r="P23" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>342</v>
+      </c>
+      <c r="R23">
+        <v>508656641</v>
+      </c>
+      <c r="S23" s="16">
+        <v>46083.818749999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" t="e">
+        <f>VLOOKUP(C24,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>293</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>22</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
+        <v>258</v>
+      </c>
+      <c r="M24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N24" t="s">
+        <v>342</v>
+      </c>
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>342</v>
+      </c>
+      <c r="R24">
+        <v>569007478</v>
+      </c>
+      <c r="S24" s="16">
+        <v>46084.039583333331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" t="e">
+        <f>VLOOKUP(C25,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>293</v>
+      </c>
+      <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>342</v>
+      </c>
+      <c r="M25" t="s">
+        <v>342</v>
+      </c>
+      <c r="N25" t="s">
+        <v>342</v>
+      </c>
+      <c r="O25" t="s">
+        <v>269</v>
+      </c>
+      <c r="P25" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>342</v>
+      </c>
+      <c r="R25">
+        <v>509288074</v>
+      </c>
+      <c r="S25" s="16">
+        <v>46084.125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" t="e">
+        <f>VLOOKUP(C26,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>293</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>342</v>
+      </c>
+      <c r="M26" t="s">
+        <v>342</v>
+      </c>
+      <c r="N26" t="s">
+        <v>342</v>
+      </c>
+      <c r="O26" t="s">
+        <v>269</v>
+      </c>
+      <c r="P26" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>342</v>
+      </c>
+      <c r="R26">
+        <v>509288074</v>
+      </c>
+      <c r="S26" s="16">
+        <v>46084.125694444447</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" t="e">
+        <f>VLOOKUP(C27,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>269</v>
+      </c>
+      <c r="M27" t="s">
+        <v>342</v>
+      </c>
+      <c r="N27" t="s">
+        <v>342</v>
+      </c>
+      <c r="O27" t="s">
+        <v>342</v>
+      </c>
+      <c r="P27" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>342</v>
+      </c>
+      <c r="R27">
+        <v>509288074</v>
+      </c>
+      <c r="S27" s="16">
+        <v>46084.125694444447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>46085</v>
+      </c>
+      <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s">
+        <v>232</v>
+      </c>
+      <c r="D28" t="e">
+        <f>VLOOKUP(C28,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
+        <v>342</v>
+      </c>
+      <c r="N28" t="s">
+        <v>342</v>
+      </c>
+      <c r="O28" t="s">
+        <v>23</v>
+      </c>
+      <c r="P28" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>342</v>
+      </c>
+      <c r="R28" t="s">
+        <v>349</v>
+      </c>
+      <c r="S28" s="16">
+        <v>46085.472638888888</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D29" t="e">
+        <f>VLOOKUP(C29,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>13</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>11</v>
+      </c>
+      <c r="M29" t="s">
+        <v>342</v>
+      </c>
+      <c r="N29" t="s">
+        <v>342</v>
+      </c>
+      <c r="O29" t="s">
+        <v>342</v>
+      </c>
+      <c r="P29" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>342</v>
+      </c>
+      <c r="R29">
+        <v>504227514</v>
+      </c>
+      <c r="S29" s="16">
+        <v>46085.475717592592</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>46085</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" t="e">
+        <f>VLOOKUP(C30,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H30">
+        <v>11</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>350</v>
+      </c>
+      <c r="M30" t="s">
+        <v>342</v>
+      </c>
+      <c r="N30" t="s">
+        <v>342</v>
+      </c>
+      <c r="O30" t="s">
+        <v>314</v>
+      </c>
+      <c r="P30" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>342</v>
+      </c>
+      <c r="R30">
+        <v>509288074</v>
+      </c>
+      <c r="S30" s="16">
+        <v>46085.510625000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>46085</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>194</v>
+      </c>
+      <c r="D31" t="e">
+        <f>VLOOKUP(C31,'Project Planning Updated'!B:B,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>342</v>
+      </c>
+      <c r="M31" t="s">
+        <v>342</v>
+      </c>
+      <c r="N31" t="s">
+        <v>342</v>
+      </c>
+      <c r="O31" t="s">
+        <v>342</v>
+      </c>
+      <c r="P31" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>342</v>
+      </c>
+      <c r="R31">
+        <v>509288074</v>
+      </c>
+      <c r="S31" s="16">
+        <v>46085.510833333334</v>
       </c>
     </row>
   </sheetData>

--- a/PPM App Data.xlsx
+++ b/PPM App Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/928dbb3f54bde61d/Documents/AMC/PPM App final version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F59E83B2-0F2A-4C11-9B64-2952A67589FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{F59E83B2-0F2A-4C11-9B64-2952A67589FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5635CDDE-0AFB-4533-880E-104CB7DFA253}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Planning Updated" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Inputs" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Planning Updated'!$A$1:$Z$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Planning Updated'!$A$1:$Z$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Team!$B$1:$I$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="438">
   <si>
     <t>phone</t>
   </si>
@@ -1348,6 +1348,12 @@
   </si>
   <si>
     <t>AHU;VRF;Packaged</t>
+  </si>
+  <si>
+    <t>Seih Al Salam - 01/03/2026</t>
+  </si>
+  <si>
+    <t>AMC11564</t>
   </si>
 </sst>
 </file>
@@ -1557,6 +1563,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1874,11 +1884,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="18.28515625" style="4" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
@@ -8751,7 +8762,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>321</v>
       </c>
@@ -8777,7 +8788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>322</v>
       </c>
@@ -8800,7 +8811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>323</v>
       </c>
@@ -8817,7 +8828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>324</v>
       </c>
@@ -8837,7 +8848,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>325</v>
       </c>
@@ -8860,7 +8871,31 @@
         <v>2</v>
       </c>
     </row>
+    <row r="102" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>436</v>
+      </c>
+      <c r="C102" t="s">
+        <v>51</v>
+      </c>
+      <c r="D102" t="s">
+        <v>437</v>
+      </c>
+      <c r="U102">
+        <v>12</v>
+      </c>
+      <c r="V102">
+        <v>49</v>
+      </c>
+      <c r="X102">
+        <v>47</v>
+      </c>
+      <c r="Y102">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:Z1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
